--- a/Selenium Project/data/test_data.xlsx
+++ b/Selenium Project/data/test_data.xlsx
@@ -5,11 +5,10 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="TrainBookingData" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="test_data" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">from_station</t>
   </si>
@@ -32,46 +31,43 @@
     <t xml:space="preserve">journey__</t>
   </si>
   <si>
+    <t xml:space="preserve">Passenger_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passenger_Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passenger_Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berth_Preference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile_Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRCTC_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARD_NUMBER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPIRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CVV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARD_HOLDER</t>
+  </si>
+  <si>
     <t xml:space="preserve">Delhi</t>
   </si>
   <si>
     <t xml:space="preserve">Lucknow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passenger_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passenger_Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passenger_Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berth_Preference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile_Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRCTC_ID </t>
-  </si>
-  <si>
-    <t xml:space="preserve">...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARD_NUMBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXPIRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CVV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARD_HOLDER</t>
   </si>
   <si>
     <t xml:space="preserve">Harsh</t>
@@ -103,7 +99,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -134,13 +130,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -189,10 +178,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -201,19 +198,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,39 +395,96 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="24.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="n">
+    <row r="2" customFormat="false" ht="24.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>46172</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>9876543210</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>4111111111111111</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -449,107 +495,4 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="20.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="5" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>9876543210</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>4111111111111111</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>